--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes-y-antartica.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>40215.17</v>
+        <v>39927.07</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>80430.33</v>
+        <v>79992.33</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>77667.38</v>
+        <v>75622.14</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39351.07</v>
+        <v>39644.24</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>27523.12</v>
+        <v>27728.17</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>56081.08</v>
+        <v>56259.57</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>77967.7</v>
+        <v>78882.3</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>37182.55</v>
+        <v>37618.72</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>38545.06</v>
+        <v>38997.21</v>
       </c>
     </row>
   </sheetData>
